--- a/data/raw/inventory/Week 28/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -2891,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2903,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>11</v>
@@ -2950,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2965,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3077,7 +3065,7 @@
         <v>33</v>
       </c>
       <c r="F43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3089,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>33</v>
@@ -3136,7 +3124,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F44" t="n">
         <v>22</v>
@@ -3151,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3198,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
         <v>18</v>
@@ -3213,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3446,10 +3434,10 @@
         </is>
       </c>
       <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
         <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -3464,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3694,7 +3682,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F53" t="n">
         <v>4</v>
@@ -3709,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -4565,19 +4553,19 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -5247,7 +5235,7 @@
         <v>35</v>
       </c>
       <c r="F78" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -5259,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>36</v>
@@ -9336,7 +9324,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -9351,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
         <v>1</v>
-      </c>
-      <c r="K144" t="n">
-        <v>2</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -10762,10 +10750,10 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F167" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10777,13 +10765,13 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -12746,7 +12734,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" t="n">
         <v>2</v>
@@ -12761,10 +12749,10 @@
         <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -14854,7 +14842,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F233" t="n">
         <v>732</v>
@@ -14869,13 +14857,13 @@
         <v>5</v>
       </c>
       <c r="J233" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K233" t="n">
         <v>766</v>
       </c>
       <c r="L233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -17210,10 +17198,10 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F271" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -17228,7 +17216,7 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -17275,7 +17263,7 @@
         <v>65</v>
       </c>
       <c r="F272" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G272" t="n">
         <v>36</v>
@@ -17287,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K272" t="n">
         <v>66</v>
@@ -17461,7 +17449,7 @@
         <v>72</v>
       </c>
       <c r="F275" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -17473,7 +17461,7 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" t="n">
         <v>72</v>
@@ -18763,7 +18751,7 @@
         <v>63</v>
       </c>
       <c r="F296" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -18775,7 +18763,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K296" t="n">
         <v>63</v>
@@ -19008,7 +18996,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F300" t="n">
         <v>198</v>
@@ -19023,10 +19011,10 @@
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -19088,10 +19076,10 @@
         <v>1</v>
       </c>
       <c r="K301" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M301" t="n">
         <v>0</v>
@@ -19318,10 +19306,10 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F305" t="n">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
@@ -19333,13 +19321,13 @@
         <v>0</v>
       </c>
       <c r="J305" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K305" t="n">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="L305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M305" t="n">
         <v>1</v>
@@ -19380,10 +19368,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F306" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G306" t="n">
         <v>0</v>
@@ -19398,7 +19386,7 @@
         <v>3</v>
       </c>
       <c r="K306" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -19566,10 +19554,10 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F309" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -19581,10 +19569,10 @@
         <v>1</v>
       </c>
       <c r="J309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K309" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L309" t="n">
         <v>1</v>
@@ -19876,7 +19864,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -19891,10 +19879,10 @@
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -19941,7 +19929,7 @@
         <v>6</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -19953,7 +19941,7 @@
         <v>0</v>
       </c>
       <c r="J315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K315" t="n">
         <v>6</v>
@@ -20186,7 +20174,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F319" t="n">
         <v>2</v>
@@ -20201,10 +20189,10 @@
         <v>0</v>
       </c>
       <c r="J319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K319" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -20372,7 +20360,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F322" t="n">
         <v>20</v>
@@ -20387,10 +20375,10 @@
         <v>0</v>
       </c>
       <c r="J322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -20496,7 +20484,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -20511,10 +20499,10 @@
         <v>0</v>
       </c>
       <c r="J324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -22173,7 +22161,7 @@
         <v>9</v>
       </c>
       <c r="F351" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
@@ -22185,7 +22173,7 @@
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K351" t="n">
         <v>9</v>
@@ -25704,10 +25692,10 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F408" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G408" t="n">
         <v>0</v>
@@ -25719,10 +25707,10 @@
         <v>0</v>
       </c>
       <c r="J408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K408" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -26138,7 +26126,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F415" t="n">
         <v>9</v>
@@ -26153,10 +26141,10 @@
         <v>0</v>
       </c>
       <c r="J415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -26528,10 +26516,10 @@
         <v>0</v>
       </c>
       <c r="K421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M421" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 28/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P424"/>
+  <dimension ref="A1:P423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,13 +585,13 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -771,13 +771,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F42" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>22</v>
       </c>
       <c r="F44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>22</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F45" t="n">
         <v>18</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
         <v>13</v>
       </c>
       <c r="F52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>13</v>
@@ -3685,19 +3685,19 @@
         <v>138</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G53" t="n">
         <v>90</v>
       </c>
       <c r="H53" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
         <v>139</v>
@@ -3871,13 +3871,13 @@
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F57" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3945,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4178,16 +4178,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
         <v>4</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F76" t="n">
         <v>21</v>
@@ -5123,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F78" t="n">
         <v>30</v>
@@ -5247,13 +5247,13 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>9</v>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F83" t="n">
         <v>12</v>
@@ -5557,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>18</v>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F131" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G131" t="n">
         <v>150</v>
@@ -8533,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F132" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G132" t="n">
         <v>2</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -8908,10 +8908,10 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F162" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10505,7 +10505,7 @@
         <v>83</v>
       </c>
       <c r="F163" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>84</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F164" t="n">
         <v>19</v>
@@ -10579,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F166" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G166" t="n">
         <v>5</v>
@@ -10706,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -10753,19 +10753,19 @@
         <v>33</v>
       </c>
       <c r="F167" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
         <v>33</v>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F168" t="n">
         <v>4</v>
@@ -10827,10 +10827,10 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -10951,10 +10951,10 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -11125,13 +11125,13 @@
         <v>9</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G173" t="n">
         <v>4</v>
       </c>
       <c r="H173" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
@@ -11807,7 +11807,7 @@
         <v>6</v>
       </c>
       <c r="F184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -11819,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K184" t="n">
         <v>6</v>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F199" t="n">
         <v>2</v>
@@ -12749,10 +12749,10 @@
         <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -12796,7 +12796,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F200" t="n">
         <v>2</v>
@@ -12811,10 +12811,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -12982,10 +12982,10 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F203" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -13000,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -13047,13 +13047,13 @@
         <v>7</v>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G204" t="n">
         <v>3</v>
       </c>
       <c r="H204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -13109,13 +13109,13 @@
         <v>10</v>
       </c>
       <c r="F205" t="n">
+        <v>7</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
         <v>2</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" t="n">
-        <v>7</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -14287,13 +14287,13 @@
         <v>2</v>
       </c>
       <c r="F224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I224" t="n">
         <v>0</v>
@@ -14473,13 +14473,13 @@
         <v>9</v>
       </c>
       <c r="F227" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G227" t="n">
         <v>2</v>
       </c>
       <c r="H227" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -14594,16 +14594,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G229" t="n">
         <v>5</v>
       </c>
       <c r="H229" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -14659,13 +14659,13 @@
         <v>3</v>
       </c>
       <c r="F230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="F233" t="n">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -14857,13 +14857,13 @@
         <v>5</v>
       </c>
       <c r="J233" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K233" t="n">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="L233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -14907,19 +14907,19 @@
         <v>23</v>
       </c>
       <c r="F234" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K234" t="n">
         <v>23</v>
@@ -17074,10 +17074,10 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F269" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -17089,10 +17089,10 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -17198,10 +17198,10 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F271" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -17213,10 +17213,10 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K271" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -17260,28 +17260,28 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F272" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G272" t="n">
         <v>36</v>
       </c>
       <c r="H272" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K272" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M272" t="n">
         <v>1</v>
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F275" t="n">
         <v>71</v>
@@ -17461,10 +17461,10 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -17511,13 +17511,13 @@
         <v>4</v>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I276" t="n">
         <v>0</v>
@@ -17818,10 +17818,10 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F281" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -17833,10 +17833,10 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K281" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L281" t="n">
         <v>2</v>
@@ -17942,25 +17942,25 @@
         </is>
       </c>
       <c r="E283" t="n">
+        <v>21</v>
+      </c>
+      <c r="F283" t="n">
+        <v>20</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
         <v>22</v>
-      </c>
-      <c r="F283" t="n">
-        <v>16</v>
-      </c>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
-      <c r="H283" t="n">
-        <v>6</v>
-      </c>
-      <c r="I283" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" t="n">
-        <v>23</v>
       </c>
       <c r="L283" t="n">
         <v>1</v>
@@ -18007,13 +18007,13 @@
         <v>7</v>
       </c>
       <c r="F284" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I284" t="n">
         <v>0</v>
@@ -18109,12 +18109,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>FBO74838</t>
+          <t>FBO74950</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>B09BBK2LV4</t>
+          <t>B09GYMBKMQ</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>AR11360</t>
+          <t>AX2429</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -18171,12 +18171,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>FBO74950</t>
+          <t>FBO74969</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>B09GYMBKMQ</t>
+          <t>B09G6GKGL4</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>AX2429</t>
+          <t>ES5136</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -18233,12 +18233,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>FBO74969</t>
+          <t>FBO75077</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>B09G6GKGL4</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18248,20 +18248,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ES5136</t>
+          <t>FS5792</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -18270,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -18295,12 +18295,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>FBO75077</t>
+          <t>FBO75153</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B0975TDMW6</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18310,20 +18310,20 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>FS5792</t>
+          <t>FS5855</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F289" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -18357,12 +18357,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>FBO75153</t>
+          <t>FBO75320</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>B0975TDMW6</t>
+          <t>B09NC2NFR9</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18372,20 +18372,20 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>FS5855</t>
+          <t>FS5901</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I290" t="n">
         <v>0</v>
@@ -18394,7 +18394,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -18419,12 +18419,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>FBO75320</t>
+          <t>FBO76447</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>B09NC2NFR9</t>
+          <t>B0B75LLWV6</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18434,17 +18434,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>FS5901</t>
+          <t>AR11484</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F291" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -18453,10 +18453,10 @@
         <v>0</v>
       </c>
       <c r="J291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -18481,12 +18481,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FBO76447</t>
+          <t>FBO76876</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>B0B75LLWV6</t>
+          <t>B0769YW2KN</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18496,20 +18496,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>AR11484</t>
+          <t>ME3154</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G292" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -18518,7 +18518,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -18543,12 +18543,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FBO76876</t>
+          <t>FBO77014</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>B0769YW2KN</t>
+          <t>B00CJ06DYG</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18558,20 +18558,20 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ME3154</t>
+          <t>AX1350</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
       </c>
       <c r="H293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I293" t="n">
         <v>0</v>
@@ -18580,7 +18580,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -18605,12 +18605,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FBO77014</t>
+          <t>FBO77065</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>B00CJ06DYG</t>
+          <t>B00Z52HG6O</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18620,11 +18620,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>AX1350</t>
+          <t>MK3197</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -18633,7 +18633,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I294" t="n">
         <v>0</v>
@@ -18642,7 +18642,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -18667,12 +18667,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>FBO77065</t>
+          <t>FBP74728</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>B00Z52HG6O</t>
+          <t>B078Y2PJL4</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18682,14 +18682,14 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>MK3197</t>
+          <t>BQ3181</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -18704,7 +18704,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -18729,12 +18729,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>FBP74728</t>
+          <t>FBP75260</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>B078Y2PJL4</t>
+          <t>B00DUCIK7U</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18744,14 +18744,14 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>BQ3181</t>
+          <t>CH2882</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="F296" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -18763,10 +18763,10 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K296" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -18791,12 +18791,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>FBP75260</t>
+          <t>FBP75458</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>B00DUCIK7U</t>
+          <t>B07RPQWF6B</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18806,11 +18806,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>CH2882</t>
+          <t>BQ3502</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="J297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -18853,12 +18853,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>FBP75458</t>
+          <t>FBS66633</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>B07RPQWF6B</t>
+          <t>B00AFTT8KE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18868,14 +18868,14 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>BQ3502</t>
+          <t>ES3284</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -18887,10 +18887,10 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K298" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -18915,12 +18915,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>FBS66633</t>
+          <t>FBS66636</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>B00AFTT8KE</t>
+          <t>B004D4S7AY</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18930,14 +18930,14 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ES3284</t>
+          <t>ES2811</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="F299" t="n">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -18949,16 +18949,16 @@
         <v>0</v>
       </c>
       <c r="J299" t="n">
+        <v>2</v>
+      </c>
+      <c r="K299" t="n">
+        <v>198</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" t="n">
         <v>1</v>
-      </c>
-      <c r="K299" t="n">
-        <v>14</v>
-      </c>
-      <c r="L299" t="n">
-        <v>0</v>
-      </c>
-      <c r="M299" t="n">
-        <v>0</v>
       </c>
       <c r="N299" t="inlineStr">
         <is>
@@ -18977,12 +18977,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>FBS66636</t>
+          <t>FBS66640</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>B004D4S7AY</t>
+          <t>B00AFTTQ8I</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18992,35 +18992,35 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ES2811</t>
+          <t>FS4813</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="F300" t="n">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H300" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I300" t="n">
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K300" t="n">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -19039,12 +19039,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>FBS66640</t>
+          <t>FBS66648</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>B00AFTTQ8I</t>
+          <t>B00AFTTQQ0</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -19054,32 +19054,32 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>FS4813</t>
+          <t>FS4812</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I301" t="n">
         <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>0</v>
@@ -19101,12 +19101,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>FBS66648</t>
+          <t>FBS66654</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>B00AFTTQQ0</t>
+          <t>B00FF8CDSO</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -19116,11 +19116,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>FS4812</t>
+          <t>ES3405</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -19129,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -19138,7 +19138,7 @@
         <v>0</v>
       </c>
       <c r="K302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -19163,12 +19163,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>FBS66654</t>
+          <t>FBS66968</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>B00FF8CDSO</t>
+          <t>B00STAYV6C</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -19178,11 +19178,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ES3405</t>
+          <t>FS5061</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -19191,7 +19191,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -19225,12 +19225,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>FBS66968</t>
+          <t>FBS66974</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>B00STAYV6C</t>
+          <t>B008AXYWHQ</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19240,35 +19240,35 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>FS5061</t>
+          <t>JR1401</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I304" t="n">
         <v>0</v>
       </c>
       <c r="J304" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K304" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
@@ -19287,12 +19287,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>FBS66974</t>
+          <t>FBS66987</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>B008AXYWHQ</t>
+          <t>B017SN1OI8</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19302,35 +19302,35 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>JR1401</t>
+          <t>FS5151</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>822</v>
+        <v>618</v>
       </c>
       <c r="F305" t="n">
-        <v>776</v>
+        <v>616</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
       </c>
       <c r="H305" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I305" t="n">
         <v>0</v>
       </c>
       <c r="J305" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K305" t="n">
-        <v>824</v>
+        <v>618</v>
       </c>
       <c r="L305" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N305" t="inlineStr">
         <is>
@@ -19349,12 +19349,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>FBS66987</t>
+          <t>FBS66995</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>B017SN1OI8</t>
+          <t>B00PW3J8LM</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19364,17 +19364,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>FS5151</t>
+          <t>ME3061</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>620</v>
+        <v>7</v>
       </c>
       <c r="F306" t="n">
-        <v>617</v>
+        <v>5</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -19383,10 +19383,10 @@
         <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>620</v>
+        <v>7</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -19411,12 +19411,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>FBS66995</t>
+          <t>FBS67266</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>B00PW3J8LM</t>
+          <t>B0058XWUHA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19426,29 +19426,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ME3061</t>
+          <t>MK5491</t>
         </is>
       </c>
       <c r="E307" t="n">
+        <v>9</v>
+      </c>
+      <c r="F307" t="n">
         <v>7</v>
       </c>
-      <c r="F307" t="n">
-        <v>5</v>
-      </c>
       <c r="G307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307" t="n">
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -19473,12 +19473,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>FBS67266</t>
+          <t>FBS67801</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>B0058XWUHA</t>
+          <t>B00HVBJ6W4</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19488,35 +19488,35 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>MK5491</t>
+          <t>ES3466</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>9</v>
+        <v>434</v>
       </c>
       <c r="F308" t="n">
-        <v>8</v>
+        <v>412</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
       </c>
       <c r="H308" t="n">
+        <v>15</v>
+      </c>
+      <c r="I308" t="n">
         <v>1</v>
       </c>
-      <c r="I308" t="n">
-        <v>0</v>
-      </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K308" t="n">
-        <v>9</v>
+        <v>434</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N308" t="inlineStr">
         <is>
@@ -19535,12 +19535,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>FBS67801</t>
+          <t>FBS67860</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>B00HVBJ6W4</t>
+          <t>B077SN2LNP</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19550,35 +19550,35 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ES3466</t>
+          <t>MK8603</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>429</v>
+        <v>5</v>
       </c>
       <c r="F309" t="n">
-        <v>407</v>
+        <v>5</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J309" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K309" t="n">
-        <v>430</v>
+        <v>5</v>
       </c>
       <c r="L309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
@@ -19597,12 +19597,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>FBS67860</t>
+          <t>FBS69548</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>B077SN2LNP</t>
+          <t>B012R0UNAW</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19612,14 +19612,14 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>MK8603</t>
+          <t>AR1926</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F310" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -19659,12 +19659,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>FBS69548</t>
+          <t>FBS69567</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>B012R0UNAW</t>
+          <t>B00786VY22</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19674,14 +19674,14 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>AR1926</t>
+          <t>AX2101</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -19693,10 +19693,10 @@
         <v>0</v>
       </c>
       <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
         <v>1</v>
-      </c>
-      <c r="K311" t="n">
-        <v>4</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -19721,12 +19721,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>FBS69567</t>
+          <t>FBS69579</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>B00786VY22</t>
+          <t>B01MTYS3BW</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19736,14 +19736,14 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>AX2101</t>
+          <t>DZ7395</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G312" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -19783,12 +19783,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>FBS69579</t>
+          <t>FBS69614</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>B01MTYS3BW</t>
+          <t>B00944CXEY</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19798,20 +19798,20 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>DZ7395</t>
+          <t>MK3190</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F313" t="n">
         <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I313" t="n">
         <v>0</v>
@@ -19820,10 +19820,10 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
+        <v>7</v>
+      </c>
+      <c r="L313" t="n">
         <v>1</v>
-      </c>
-      <c r="L313" t="n">
-        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>0</v>
@@ -19845,12 +19845,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>FBS69614</t>
+          <t>FBS70769</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>B00944CXEY</t>
+          <t>B07M7P7VLX</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19860,29 +19860,29 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>MK3190</t>
+          <t>ES4519</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="n">
         <v>4</v>
       </c>
-      <c r="H314" t="n">
-        <v>2</v>
-      </c>
       <c r="I314" t="n">
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -19907,12 +19907,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>FBS70769</t>
+          <t>FBS70827</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>B07M7P7VLX</t>
+          <t>B07MM5MH6F</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19922,14 +19922,14 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ES4519</t>
+          <t>FS5512</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -19941,10 +19941,10 @@
         <v>0</v>
       </c>
       <c r="J315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -19969,12 +19969,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>FBS70827</t>
+          <t>FBS71628</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>B07MM5MH6F</t>
+          <t>B07RZ1R1HJ</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19984,20 +19984,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>FS5512</t>
+          <t>ES4628</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>25</v>
       </c>
       <c r="F316" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -20031,12 +20031,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>FBS71628</t>
+          <t>FBS72002</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>B07RZ1R1HJ</t>
+          <t>B00CMWR0K2</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -20046,14 +20046,14 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ES4628</t>
+          <t>AR1676</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F317" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G317" t="n">
         <v>0</v>
@@ -20068,7 +20068,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -20093,12 +20093,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>FBS72002</t>
+          <t>FBS73952</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>B00CMWR0K2</t>
+          <t>B00EVZ83J0</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -20108,14 +20108,14 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>AR1676</t>
+          <t>CH2885</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
@@ -20130,7 +20130,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -20155,12 +20155,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>FBS73952</t>
+          <t>FBS74241</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>B00EVZ83J0</t>
+          <t>B086K654H9</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -20170,14 +20170,14 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>CH2885</t>
+          <t>ES4879</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G319" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -20217,12 +20217,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>FBS74241</t>
+          <t>FBS74251</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>B086K654H9</t>
+          <t>B01GZZYSRO</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20232,20 +20232,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ES4879</t>
+          <t>AR1979</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I320" t="n">
         <v>0</v>
@@ -20254,7 +20254,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -20279,12 +20279,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>FBS74251</t>
+          <t>FBS74257</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>B01GZZYSRO</t>
+          <t>B079XB5RXH</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20294,20 +20294,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>AR1979</t>
+          <t>MK6485</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F321" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G321" t="n">
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I321" t="n">
         <v>0</v>
@@ -20316,7 +20316,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -20341,12 +20341,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>FBS74257</t>
+          <t>FBS74343</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>B079XB5RXH</t>
+          <t>B08SW1LBDF</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20356,14 +20356,14 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>MK6485</t>
+          <t>DZ4548</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F322" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G322" t="n">
         <v>0</v>
@@ -20378,7 +20378,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -20403,12 +20403,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FBS74343</t>
+          <t>FBS74358</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>B08SW1LBDF</t>
+          <t>B01KNMEVDG</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20418,14 +20418,14 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>DZ4548</t>
+          <t>FS5237</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G323" t="n">
         <v>0</v>
@@ -20440,7 +20440,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -20465,12 +20465,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>FBS74358</t>
+          <t>FBS74721</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>B01KNMEVDG</t>
+          <t>B00AMWDOEK</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20480,20 +20480,20 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>FS5237</t>
+          <t>FS4735</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I324" t="n">
         <v>0</v>
@@ -20502,7 +20502,7 @@
         <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -20527,12 +20527,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>FBS74721</t>
+          <t>FBS74758</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>B00AMWDOEK</t>
+          <t>B0846PC77Q</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20542,29 +20542,29 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>FS4735</t>
+          <t>AX2413</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F325" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G325" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
         <v>0</v>
       </c>
       <c r="J325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -20589,12 +20589,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>FBS74758</t>
+          <t>FBS74838</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>B0846PC77Q</t>
+          <t>B09BBK2LV4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20604,14 +20604,14 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AX2413</t>
+          <t>AR11360</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F326" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -20626,7 +20626,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -20651,12 +20651,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FBS74838</t>
+          <t>FBS74927</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>B09BBK2LV4</t>
+          <t>B0846Q1JT5</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20666,14 +20666,14 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AR11360</t>
+          <t>AX5901</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
@@ -20688,7 +20688,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -20713,12 +20713,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FBS74927</t>
+          <t>FBS74952</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>B0846Q1JT5</t>
+          <t>B09CSXR4TR</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20728,14 +20728,14 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AX5901</t>
+          <t>AX5911</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F328" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G328" t="n">
         <v>0</v>
@@ -20750,7 +20750,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -20775,12 +20775,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>FBS74952</t>
+          <t>FBS74972</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>B09CSXR4TR</t>
+          <t>B09GYQ4RS7</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20790,14 +20790,14 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>AX5911</t>
+          <t>ME3206</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F329" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
@@ -20812,7 +20812,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -20837,12 +20837,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>FBS74972</t>
+          <t>FBS75146</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>B09GYQ4RS7</t>
+          <t>B079DC27J5</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20852,14 +20852,14 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ME3206</t>
+          <t>FS5452</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F330" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
@@ -20874,13 +20874,13 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
@@ -20899,12 +20899,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FBS75146</t>
+          <t>FBS75260</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>B079DC27J5</t>
+          <t>B00DUCIK7U</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20914,20 +20914,20 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>FS5452</t>
+          <t>CH2882</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F331" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G331" t="n">
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I331" t="n">
         <v>0</v>
@@ -20936,13 +20936,13 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
@@ -20961,12 +20961,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>FBS75260</t>
+          <t>FBS75262</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>B00DUCIK7U</t>
+          <t>B0183NW5H6</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>CH2882</t>
+          <t>FS5164</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -21023,12 +21023,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>FBS75262</t>
+          <t>FBS75326</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>B0183NW5H6</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -21038,20 +21038,20 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>FS5164</t>
+          <t>ME3218</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H333" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -21060,7 +21060,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -21085,12 +21085,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>FBS75326</t>
+          <t>FBS75346</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B08XBYKWW3</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -21100,29 +21100,29 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ME3218</t>
+          <t>AR11338</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
       </c>
       <c r="J334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K334" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -21147,12 +21147,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>FBS75346</t>
+          <t>FBS75372</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>B08XBYKWW3</t>
+          <t>B0846PJPW9</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -21162,11 +21162,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>AR11338</t>
+          <t>AX1343</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -21175,16 +21175,16 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I335" t="n">
         <v>0</v>
       </c>
       <c r="J335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -21209,12 +21209,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>FBS75372</t>
+          <t>FBS76490</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>B0846PJPW9</t>
+          <t>B08HGVDKFH</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -21224,14 +21224,14 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>AX1343</t>
+          <t>FS5708SET</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -21246,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -21271,12 +21271,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>FBS76490</t>
+          <t>FBS76772</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>B08HGVDKFH</t>
+          <t>B0BFZRGPJ6</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21286,14 +21286,14 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>FS5708SET</t>
+          <t>AR11500</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
@@ -21308,7 +21308,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -21333,12 +21333,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>FBS76772</t>
+          <t>FBS76941</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>B0BFZRGPJ6</t>
+          <t>B0BFXL8ZP9</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21348,20 +21348,20 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>AR11500</t>
+          <t>FS5963</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G338" t="n">
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I338" t="n">
         <v>0</v>
@@ -21370,7 +21370,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -21395,12 +21395,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>FBS76941</t>
+          <t>FBS77066</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>B0BFXL8ZP9</t>
+          <t>B07QSK7DHR</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21410,20 +21410,20 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>FS5963</t>
+          <t>MK4339</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F339" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G339" t="n">
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I339" t="n">
         <v>0</v>
@@ -21432,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -21457,12 +21457,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>FBS77066</t>
+          <t>FBS77988</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>B07QSK7DHR</t>
+          <t>B0BR5DZQSN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>MK4339</t>
+          <t>DZ4627</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -21519,12 +21519,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>FBS77988</t>
+          <t>FBS77995</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>B0BR5DZQSN</t>
+          <t>B0BS4BFLZW</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21534,14 +21534,14 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>DZ4627</t>
+          <t>MK4709</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -21581,12 +21581,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>FBS77995</t>
+          <t>FBS77996</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>B0BS4BFLZW</t>
+          <t>B0BS4BHNVN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21596,14 +21596,14 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>MK4709</t>
+          <t>MK4710</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G342" t="n">
         <v>0</v>
@@ -21618,7 +21618,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -21643,12 +21643,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>FBS77996</t>
+          <t>FBS78006</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>B0BS4BHNVN</t>
+          <t>B0BQ34DFX7</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21658,14 +21658,14 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>MK4710</t>
+          <t>ES5264</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
@@ -21680,7 +21680,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -21705,12 +21705,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>FBS78006</t>
+          <t>FBS78012</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>B0BQ34DFX7</t>
+          <t>B0BQ35JRM3</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21720,14 +21720,14 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>ES5264</t>
+          <t>FS5971</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -21767,12 +21767,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>FBS78012</t>
+          <t>FBS79031</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>B0BQ35JRM3</t>
+          <t>B0C89RHY4W</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21782,20 +21782,20 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>FS5971</t>
+          <t>ES5306</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -21829,12 +21829,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>FBS79031</t>
+          <t>FBS79040</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>B0C89RHY4W</t>
+          <t>B0CCHKHCTD</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21844,20 +21844,20 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>ES5306</t>
+          <t>AR70010</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F346" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I346" t="n">
         <v>0</v>
@@ -21866,10 +21866,10 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -21891,12 +21891,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>FBS79040</t>
+          <t>FBS79048</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>B0CCHKHCTD</t>
+          <t>B0CCHHGG9B</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21906,14 +21906,14 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>AR70010</t>
+          <t>AR11575</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F347" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G347" t="n">
         <v>0</v>
@@ -21928,10 +21928,10 @@
         <v>0</v>
       </c>
       <c r="K347" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M347" t="n">
         <v>0</v>
@@ -21953,12 +21953,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>FBS79048</t>
+          <t>FBS79143</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>B0CCHHGG9B</t>
+          <t>B0CJ6ZHK1S</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21968,14 +21968,14 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>AR11575</t>
+          <t>ES5323</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F348" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G348" t="n">
         <v>0</v>
@@ -21990,7 +21990,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -22015,12 +22015,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>FBS79143</t>
+          <t>FBS79152</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>B0CJ6ZHK1S</t>
+          <t>B0CHXTNMNX</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -22030,14 +22030,14 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>ES5323</t>
+          <t>AX7151SET</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F349" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
@@ -22052,7 +22052,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -22077,12 +22077,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>FBS79152</t>
+          <t>FBS79223</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>B0CHXTNMNX</t>
+          <t>B0CFBB587Z</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -22092,14 +22092,14 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>AX7151SET</t>
+          <t>ME3253</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F350" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G350" t="n">
         <v>0</v>
@@ -22114,7 +22114,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -22139,12 +22139,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>FBS79223</t>
+          <t>FBS79224</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>B0CFBB587Z</t>
+          <t>B0CFBCTN93</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -22154,29 +22154,29 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>ME3253</t>
+          <t>ME3254</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F351" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -22201,12 +22201,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>FBS79224</t>
+          <t>FBS79283</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>B0CFBCTN93</t>
+          <t>B0CR5RR8Z6</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -22216,14 +22216,14 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>ME3254</t>
+          <t>AR11596</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G352" t="n">
         <v>0</v>
@@ -22238,7 +22238,7 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -22263,12 +22263,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>FBS79283</t>
+          <t>FBS79292</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>B0CR5RR8Z6</t>
+          <t>B0CRCTQH2C</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>AR11596</t>
+          <t>MK4805</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -22325,12 +22325,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>FBS79292</t>
+          <t>FBS79302</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>B0CRCTQH2C</t>
+          <t>B0CR5QRNQN</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22340,20 +22340,20 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>MK4805</t>
+          <t>AR60076</t>
         </is>
       </c>
       <c r="E354" t="n">
         <v>1</v>
       </c>
       <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
         <v>1</v>
-      </c>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -22387,12 +22387,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>FBS79302</t>
+          <t>FBS79303</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>B0CR5QRNQN</t>
+          <t>B0CR5RZRMH</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22402,11 +22402,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>AR60076</t>
+          <t>AR11589</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -22415,7 +22415,7 @@
         <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I355" t="n">
         <v>0</v>
@@ -22424,7 +22424,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -22449,12 +22449,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FBS79303</t>
+          <t>FBS79310</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>B0CR5RZRMH</t>
+          <t>B0CRSQDJJ5</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22464,14 +22464,14 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>AR11589</t>
+          <t>MK9152</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G356" t="n">
         <v>0</v>
@@ -22486,7 +22486,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -22511,12 +22511,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FBS79310</t>
+          <t>FBS79311</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>B0CRSQDJJ5</t>
+          <t>B0CRCZYDY6</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22526,14 +22526,14 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>MK9152</t>
+          <t>MK4817SET</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F357" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G357" t="n">
         <v>0</v>
@@ -22548,7 +22548,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -22573,12 +22573,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>FBS79311</t>
+          <t>FBS79312</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>B0CRCZYDY6</t>
+          <t>B0CRT23BD5</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22588,14 +22588,14 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>MK4817SET</t>
+          <t>MK9153</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
@@ -22610,7 +22610,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -22635,12 +22635,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>FBS79312</t>
+          <t>FBS79317</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>B0CRT23BD5</t>
+          <t>B0CR5S175Y</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22650,14 +22650,14 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>MK9153</t>
+          <t>AX2454</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G359" t="n">
         <v>0</v>
@@ -22672,7 +22672,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -22697,12 +22697,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FBS79317</t>
+          <t>FBS79319</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>B0CR5S175Y</t>
+          <t>B0CRD2CVZL</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22712,14 +22712,14 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>AX2454</t>
+          <t>ES5338</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F360" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G360" t="n">
         <v>0</v>
@@ -22731,10 +22731,10 @@
         <v>0</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K360" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -22759,12 +22759,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>FBS79319</t>
+          <t>FBS79334</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>B0CRD2CVZL</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22774,17 +22774,17 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>ES5338</t>
+          <t>FS6048</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F361" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -22796,7 +22796,7 @@
         <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -22821,12 +22821,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>FBS79334</t>
+          <t>FBS79335</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0CRD1DRXG</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22836,17 +22836,17 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>FS6048</t>
+          <t>ME3260</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F362" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -22858,7 +22858,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -22883,12 +22883,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>FBS79335</t>
+          <t>FBS79336</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>B0CRD1DRXG</t>
+          <t>B0CRD7DH79</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22898,14 +22898,14 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>ME3260</t>
+          <t>FS6045</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F363" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -22945,12 +22945,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>FBS79336</t>
+          <t>FBS79340</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>B0CRD7DH79</t>
+          <t>B0CRCYMKY8</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>FS6045</t>
+          <t>MK7474</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -23007,12 +23007,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>FBS79340</t>
+          <t>FBS79411</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>B0CRCYMKY8</t>
+          <t>B07T63ZJTR</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -23022,14 +23022,14 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>MK7474</t>
+          <t>DZ4662</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G365" t="n">
         <v>0</v>
@@ -23044,7 +23044,7 @@
         <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -23069,12 +23069,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>FBS79411</t>
+          <t>FBS79412</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>B07T63ZJTR</t>
+          <t>B07T3ZLNM3</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -23084,20 +23084,20 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>DZ4662</t>
+          <t>DZ4665</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G366" t="n">
         <v>0</v>
       </c>
       <c r="H366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I366" t="n">
         <v>0</v>
@@ -23106,7 +23106,7 @@
         <v>0</v>
       </c>
       <c r="K366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -23131,12 +23131,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>FBS79412</t>
+          <t>FBS79413</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>B07T3ZLNM3</t>
+          <t>B07T1X96CL</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -23146,11 +23146,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>DZ4665</t>
+          <t>DZ4667</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F367" t="n">
         <v>2</v>
@@ -23159,7 +23159,7 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I367" t="n">
         <v>0</v>
@@ -23168,7 +23168,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -23193,12 +23193,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>FBS79413</t>
+          <t>FBS79414</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>B07T1X96CL</t>
+          <t>B07T63MQ9G</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -23208,14 +23208,14 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>DZ4667</t>
+          <t>DZ2210SET</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -23255,12 +23255,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>FBS79414</t>
+          <t>FBS79417</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>B07T63MQ9G</t>
+          <t>B0CYNH9X11</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23270,14 +23270,14 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>DZ2210SET</t>
+          <t>AR11606</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F369" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G369" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -23317,12 +23317,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>FBS79417</t>
+          <t>FBS79421</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>B0CYNH9X11</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23332,14 +23332,14 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>AR11606</t>
+          <t>ES5349</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G370" t="n">
         <v>0</v>
@@ -23351,10 +23351,10 @@
         <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K370" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -23379,12 +23379,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>FBS79421</t>
+          <t>FBS79422</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0CZ91YKMP</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23394,29 +23394,29 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>ES5349</t>
+          <t>ES5350</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F371" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G371" t="n">
         <v>0</v>
       </c>
       <c r="H371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I371" t="n">
         <v>0</v>
       </c>
       <c r="J371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -23441,12 +23441,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>FBS79422</t>
+          <t>FBS79423</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>B0CZ91YKMP</t>
+          <t>B0CZ94B6QL</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23456,11 +23456,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>ES5350</t>
+          <t>MK4822</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F372" t="n">
         <v>3</v>
@@ -23469,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
         <v>0</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -23503,12 +23503,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>FBS79423</t>
+          <t>FBS79424</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>B0CZ94B6QL</t>
+          <t>B0CZ9BTN24</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>MK4822</t>
+          <t>MK4823</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -23565,12 +23565,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>FBS79424</t>
+          <t>FBS79425</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>B0CZ9BTN24</t>
+          <t>B0CZ9HTWNC</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23580,14 +23580,14 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>MK4823</t>
+          <t>MK4824</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F374" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G374" t="n">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -23627,12 +23627,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>FBS79425</t>
+          <t>FBS79426</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>B0CZ9HTWNC</t>
+          <t>B0CZ93JG5X</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23642,14 +23642,14 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>MK4824</t>
+          <t>MK4829</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G375" t="n">
         <v>0</v>
@@ -23664,7 +23664,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -23689,12 +23689,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>FBS79426</t>
+          <t>FBS79428</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>B0CZ93JG5X</t>
+          <t>B0CZ93BN92</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>MK4829</t>
+          <t>MK9165</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -23751,12 +23751,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>FBS79428</t>
+          <t>FBS79432</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>B0CZ93BN92</t>
+          <t>B0CZ8X8CBD</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23766,14 +23766,14 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>MK9165</t>
+          <t>FS6056</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F377" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G377" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="K377" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -23813,12 +23813,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>FBS79432</t>
+          <t>FBS79498</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>B0CZ8X8CBD</t>
+          <t>B0D9363BB2</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23828,14 +23828,14 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>FS6056</t>
+          <t>AR11623</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F378" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G378" t="n">
         <v>0</v>
@@ -23850,10 +23850,10 @@
         <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M378" t="n">
         <v>0</v>
@@ -23875,12 +23875,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>FBS79498</t>
+          <t>FBS79500</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>B0D9363BB2</t>
+          <t>B0D935TKFD</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23890,14 +23890,14 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>AR11623</t>
+          <t>AR11625</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G379" t="n">
         <v>0</v>
@@ -23915,7 +23915,7 @@
         <v>4</v>
       </c>
       <c r="L379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M379" t="n">
         <v>0</v>
@@ -23937,12 +23937,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>FBS79500</t>
+          <t>FBS79502</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>B0D935TKFD</t>
+          <t>B0D935CGMF</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23952,14 +23952,14 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AR11625</t>
+          <t>AR11635</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F380" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G380" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -23999,12 +23999,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>FBS79502</t>
+          <t>FBS79503</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>B0D935CGMF</t>
+          <t>B0D935S1B3</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -24014,14 +24014,14 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>AR11635</t>
+          <t>AR11636</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -24036,7 +24036,7 @@
         <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -24061,12 +24061,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>FBS79503</t>
+          <t>FBS79504</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>B0D935S1B3</t>
+          <t>B0D935TWSR</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -24076,14 +24076,14 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>AR11636</t>
+          <t>AR11637</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F382" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -24098,7 +24098,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -24123,12 +24123,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>FBS79504</t>
+          <t>FBS79506</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>B0D935TWSR</t>
+          <t>B0D936RRVB</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -24138,14 +24138,14 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>AR11637</t>
+          <t>AR60079</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G383" t="n">
         <v>0</v>
@@ -24160,7 +24160,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -24185,12 +24185,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>FBS79506</t>
+          <t>FBS79507</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>B0D936RRVB</t>
+          <t>B0D9345QY7</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -24200,14 +24200,14 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>AR60079</t>
+          <t>AR60080</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G384" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -24247,12 +24247,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>FBS79507</t>
+          <t>FBS79512</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>B0D9345QY7</t>
+          <t>B0D84YY632</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -24262,14 +24262,14 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>AR60080</t>
+          <t>AX4180</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G385" t="n">
         <v>0</v>
@@ -24284,7 +24284,7 @@
         <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -24309,12 +24309,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>FBS79512</t>
+          <t>FBS79513</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>B0D84YY632</t>
+          <t>B0D853Y52R</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24324,14 +24324,14 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>AX4180</t>
+          <t>AX4181</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F386" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G386" t="n">
         <v>0</v>
@@ -24346,7 +24346,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -24371,12 +24371,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>FBS79513</t>
+          <t>FBS79514</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>B0D853Y52R</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24386,14 +24386,14 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>AX4181</t>
+          <t>AX4182</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F387" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G387" t="n">
         <v>0</v>
@@ -24405,10 +24405,10 @@
         <v>0</v>
       </c>
       <c r="J387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K387" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L387" t="n">
         <v>0</v>
@@ -24433,12 +24433,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>FBS79514</t>
+          <t>FBS79515</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24448,20 +24448,20 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>AX4182</t>
+          <t>AX4183</t>
         </is>
       </c>
       <c r="E388" t="n">
+        <v>13</v>
+      </c>
+      <c r="F388" t="n">
         <v>11</v>
       </c>
-      <c r="F388" t="n">
-        <v>10</v>
-      </c>
       <c r="G388" t="n">
         <v>0</v>
       </c>
       <c r="H388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I388" t="n">
         <v>0</v>
@@ -24470,7 +24470,7 @@
         <v>1</v>
       </c>
       <c r="K388" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L388" t="n">
         <v>0</v>
@@ -24495,12 +24495,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>FBS79515</t>
+          <t>FBS79517</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0D85171BL</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24510,29 +24510,29 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>AX4183</t>
+          <t>AX5724</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F389" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
       </c>
       <c r="J389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K389" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -24557,12 +24557,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>FBS79517</t>
+          <t>FBS79518</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>B0D85171BL</t>
+          <t>B0D84YD59Y</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24572,17 +24572,17 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>AX5724</t>
+          <t>AX5725</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -24594,7 +24594,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -24619,12 +24619,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>FBS79518</t>
+          <t>FBS79521</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>B0D84YD59Y</t>
+          <t>B07T62VK1C</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24634,14 +24634,14 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>AX5725</t>
+          <t>DZ2212</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F391" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G391" t="n">
         <v>0</v>
@@ -24656,7 +24656,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -24681,12 +24681,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>FBS79521</t>
+          <t>FBS79522</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>B07T62VK1C</t>
+          <t>B07SZSVT1F</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24696,14 +24696,14 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>DZ2212</t>
+          <t>DZ2213</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
@@ -24718,7 +24718,7 @@
         <v>0</v>
       </c>
       <c r="K392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -24743,12 +24743,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>FBS79522</t>
+          <t>FBS79523</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>B07SZSVT1F</t>
+          <t>B07T1X8TKH</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24758,14 +24758,14 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>DZ2213</t>
+          <t>DZ2214</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G393" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -24805,12 +24805,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>FBS79523</t>
+          <t>FBS79524</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>B07T1X8TKH</t>
+          <t>B07T1X89FZ</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24820,14 +24820,14 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>DZ2214</t>
+          <t>DZ2215</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G394" t="n">
         <v>0</v>
@@ -24842,7 +24842,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -24867,12 +24867,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>FBS79524</t>
+          <t>FBS79539</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>B07T1X89FZ</t>
+          <t>B0D955L5S7</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24882,14 +24882,14 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>DZ2215</t>
+          <t>MK4842</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
@@ -24904,7 +24904,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -24929,12 +24929,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>FBS79539</t>
+          <t>FBS79540</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>B0D955L5S7</t>
+          <t>B0D955B6SX</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24944,14 +24944,14 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>MK4842</t>
+          <t>MK4843</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F396" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G396" t="n">
         <v>0</v>
@@ -24966,7 +24966,7 @@
         <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -24991,12 +24991,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>FBS79540</t>
+          <t>FBS79541</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>B0D955B6SX</t>
+          <t>B0D955BY7N</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -25006,14 +25006,14 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>MK4843</t>
+          <t>MK4845</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G397" t="n">
         <v>0</v>
@@ -25028,7 +25028,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -25053,12 +25053,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>FBS79541</t>
+          <t>FBS79542</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>B0D955BY7N</t>
+          <t>B0D955GP1C</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -25068,14 +25068,14 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>MK4845</t>
+          <t>MK4847</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F398" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G398" t="n">
         <v>0</v>
@@ -25090,7 +25090,7 @@
         <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -25115,12 +25115,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>FBS79542</t>
+          <t>FBS79545</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>B0D955GP1C</t>
+          <t>B0D955VQ4S</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -25130,14 +25130,14 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>MK4847</t>
+          <t>MK7488</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
@@ -25152,7 +25152,7 @@
         <v>0</v>
       </c>
       <c r="K399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -25177,12 +25177,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>FBS79545</t>
+          <t>FBS79556</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>B0D955VQ4S</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -25192,20 +25192,20 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>MK7488</t>
+          <t>MK9177</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G400" t="n">
         <v>0</v>
       </c>
       <c r="H400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I400" t="n">
         <v>0</v>
@@ -25214,7 +25214,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -25239,12 +25239,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>FBS79556</t>
+          <t>FBS79557</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>B0D955YGX7</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -25254,20 +25254,20 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>MK9177</t>
+          <t>MK9178</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F401" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G401" t="n">
         <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I401" t="n">
         <v>0</v>
@@ -25276,10 +25276,10 @@
         <v>0</v>
       </c>
       <c r="K401" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M401" t="n">
         <v>0</v>
@@ -25301,12 +25301,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>FBS79557</t>
+          <t>FBS79558</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25316,35 +25316,35 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>MK9178</t>
+          <t>MK9179</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F402" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G402" t="n">
         <v>0</v>
       </c>
       <c r="H402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I402" t="n">
         <v>0</v>
       </c>
       <c r="J402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" t="n">
+        <v>8</v>
+      </c>
+      <c r="L402" t="n">
+        <v>0</v>
+      </c>
+      <c r="M402" t="n">
         <v>1</v>
-      </c>
-      <c r="K402" t="n">
-        <v>5</v>
-      </c>
-      <c r="L402" t="n">
-        <v>1</v>
-      </c>
-      <c r="M402" t="n">
-        <v>0</v>
       </c>
       <c r="N402" t="inlineStr">
         <is>
@@ -25363,12 +25363,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>FBS79558</t>
+          <t>FBS79561</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0D955H882</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25378,35 +25378,35 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>MK9179</t>
+          <t>MK9185</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F403" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G403" t="n">
         <v>0</v>
       </c>
       <c r="H403" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I403" t="n">
         <v>0</v>
       </c>
       <c r="J403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K403" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N403" t="inlineStr">
         <is>
@@ -25425,12 +25425,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>FBS79561</t>
+          <t>FBS79618</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>B0D955H882</t>
+          <t>B0DJ2XCDJ1</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25440,14 +25440,14 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>MK9185</t>
+          <t>AR11639</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G404" t="n">
         <v>0</v>
@@ -25462,7 +25462,7 @@
         <v>0</v>
       </c>
       <c r="K404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L404" t="n">
         <v>0</v>
@@ -25487,12 +25487,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>FBS79618</t>
+          <t>FBS79624</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>B0DJ2XCDJ1</t>
+          <t>B0DKJHJV6T</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25502,14 +25502,14 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>AR11639</t>
+          <t>AX2460</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
@@ -25524,7 +25524,7 @@
         <v>0</v>
       </c>
       <c r="K405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
@@ -25549,12 +25549,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>FBS79624</t>
+          <t>FBS79625</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>B0DKJHJV6T</t>
+          <t>B0DKJH623H</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25564,11 +25564,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>AX2460</t>
+          <t>AX2461</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F406" t="n">
         <v>0</v>
@@ -25577,7 +25577,7 @@
         <v>0</v>
       </c>
       <c r="H406" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I406" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="K406" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -25611,12 +25611,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>FBS79625</t>
+          <t>FBS79627</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>B0DKJH623H</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25626,20 +25626,20 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>AX2461</t>
+          <t>AX4184</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I407" t="n">
         <v>0</v>
@@ -25648,7 +25648,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
@@ -25673,12 +25673,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>FBS79627</t>
+          <t>FBS79628</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0DKJBJBX6</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25688,29 +25688,29 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>AX4184</t>
+          <t>AX7163SET</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="F408" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G408" t="n">
         <v>0</v>
       </c>
       <c r="H408" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I408" t="n">
         <v>0</v>
       </c>
       <c r="J408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K408" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -25735,12 +25735,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>FBS79628</t>
+          <t>FBS79629</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>B0DKJBJBX6</t>
+          <t>B0DJ2X1477</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25750,14 +25750,14 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>AX7163SET</t>
+          <t>ES5380</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F409" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
         <v>0</v>
       </c>
       <c r="K409" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -25797,12 +25797,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>FBS79629</t>
+          <t>FBS79630</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>B0DJ2X1477</t>
+          <t>B0DJ2YM76K</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25812,14 +25812,14 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>ES5380</t>
+          <t>ES5381</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G410" t="n">
         <v>0</v>
@@ -25834,7 +25834,7 @@
         <v>0</v>
       </c>
       <c r="K410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L410" t="n">
         <v>0</v>
@@ -25859,12 +25859,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>FBS79630</t>
+          <t>FBS79632</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>B0DJ2YM76K</t>
+          <t>B0DJ2Y1BG6</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25874,14 +25874,14 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ES5381</t>
+          <t>ES5387SET</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G411" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -25921,12 +25921,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>FBS79632</t>
+          <t>FBS79636</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>B0DJ2Y1BG6</t>
+          <t>B0D9ZN5NBD</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25936,17 +25936,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>ES5387SET</t>
+          <t>FS6085</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F412" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -25958,7 +25958,7 @@
         <v>0</v>
       </c>
       <c r="K412" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -25983,12 +25983,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>FBS79636</t>
+          <t>FBS79637</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>B0D9ZN5NBD</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25998,20 +25998,20 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>FS6085</t>
+          <t>FS6086</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G413" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I413" t="n">
         <v>0</v>
@@ -26020,7 +26020,7 @@
         <v>0</v>
       </c>
       <c r="K413" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -26045,12 +26045,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>FBS79637</t>
+          <t>FBS79638</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>B0DC64BD5R</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -26060,20 +26060,20 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>FS6086</t>
+          <t>FS6087</t>
         </is>
       </c>
       <c r="E414" t="n">
         <v>14</v>
       </c>
       <c r="F414" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G414" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H414" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I414" t="n">
         <v>0</v>
@@ -26107,12 +26107,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>FBS79638</t>
+          <t>FBS79642</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0DJ2Y4J4Q</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -26122,17 +26122,17 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>FS6087</t>
+          <t>ME3265</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F415" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H415" t="n">
         <v>1</v>
@@ -26141,10 +26141,10 @@
         <v>0</v>
       </c>
       <c r="J415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K415" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -26169,12 +26169,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>FBS79642</t>
+          <t>FBS79643</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>B0DJ2Y4J4Q</t>
+          <t>B0DJ2XNSD2</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -26184,20 +26184,20 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>ME3265</t>
+          <t>ME3266</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F416" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G416" t="n">
         <v>0</v>
       </c>
       <c r="H416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I416" t="n">
         <v>0</v>
@@ -26206,7 +26206,7 @@
         <v>0</v>
       </c>
       <c r="K416" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -26231,12 +26231,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>FBS79643</t>
+          <t>FBS79644</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>B0DJ2XNSD2</t>
+          <t>B0DJ2WJ9R7</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -26246,14 +26246,14 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>ME3266</t>
+          <t>MK4863</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F417" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G417" t="n">
         <v>0</v>
@@ -26268,7 +26268,7 @@
         <v>0</v>
       </c>
       <c r="K417" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -26293,12 +26293,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>FBS79644</t>
+          <t>FBS79645</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>B0DJ2WJ9R7</t>
+          <t>B0DJ2WNH1Y</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -26308,14 +26308,14 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>MK4863</t>
+          <t>MK4864</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="K418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -26355,12 +26355,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>FBS79645</t>
+          <t>FBS79646</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>B0DJ2WNH1Y</t>
+          <t>B0DJ2XK4NR</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26370,14 +26370,14 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>MK4864</t>
+          <t>MK4870</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -26392,7 +26392,7 @@
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -26417,12 +26417,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>FBS79646</t>
+          <t>FBS79647</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>B0DJ2XK4NR</t>
+          <t>B0DJ2XDV59</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26432,14 +26432,14 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>MK4870</t>
+          <t>MK4873</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G420" t="n">
         <v>0</v>
@@ -26454,7 +26454,7 @@
         <v>0</v>
       </c>
       <c r="K420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -26479,12 +26479,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>FBS79647</t>
+          <t>FBS79649</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>B0DJ2XDV59</t>
+          <t>B0DJ2W8W79</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26494,14 +26494,14 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>MK4873</t>
+          <t>MK9191</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F421" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G421" t="n">
         <v>0</v>
@@ -26516,7 +26516,7 @@
         <v>0</v>
       </c>
       <c r="K421" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L421" t="n">
         <v>0</v>
@@ -26541,12 +26541,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>FBS79649</t>
+          <t>FBS79650</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>B0DJ2W8W79</t>
+          <t>B0DJ2XWYX7</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26556,14 +26556,14 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>MK9191</t>
+          <t>MK9192</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F422" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G422" t="n">
         <v>0</v>
@@ -26578,7 +26578,7 @@
         <v>0</v>
       </c>
       <c r="K422" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L422" t="n">
         <v>0</v>
@@ -26603,12 +26603,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>FBS79650</t>
+          <t>FBS79651</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>B0DJ2XWYX7</t>
+          <t>B0DJ2WP1M5</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26618,14 +26618,14 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>MK9192</t>
+          <t>MK9193</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G423" t="n">
         <v>0</v>
@@ -26640,7 +26640,7 @@
         <v>0</v>
       </c>
       <c r="K423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -26659,68 +26659,6 @@
         </is>
       </c>
       <c r="P423" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>FBS79651</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>B0DJ2WP1M5</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>MK9193</t>
-        </is>
-      </c>
-      <c r="E424" t="n">
-        <v>4</v>
-      </c>
-      <c r="F424" t="n">
-        <v>4</v>
-      </c>
-      <c r="G424" t="n">
-        <v>0</v>
-      </c>
-      <c r="H424" t="n">
-        <v>0</v>
-      </c>
-      <c r="I424" t="n">
-        <v>0</v>
-      </c>
-      <c r="J424" t="n">
-        <v>0</v>
-      </c>
-      <c r="K424" t="n">
-        <v>4</v>
-      </c>
-      <c r="L424" t="n">
-        <v>0</v>
-      </c>
-      <c r="M424" t="n">
-        <v>0</v>
-      </c>
-      <c r="N424" t="inlineStr">
-        <is>
-          <t>CAMBIUMRETAIL</t>
-        </is>
-      </c>
-      <c r="O424" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="P424" t="n">
         <v>28</v>
       </c>
     </row>
